--- a/software_developer_forms/023_tech_api_offerings_developer_satisfaction_questionnaire--software_developer_forms.xlsx
+++ b/software_developer_forms/023_tech_api_offerings_developer_satisfaction_questionnaire--software_developer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Features Other</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Support Other</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Frequent Use Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Pricing Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Security Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Usability Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Usability Features Other</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Api Developers Other</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1409,17 +1409,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>api_features_choices</t>
+          <t>api_support_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>api_keys_with_a_refresh_token</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>API Keys with a refresh token</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1482,29 +1482,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>api_support_choices</t>
+          <t>api_frequent_use_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1567,29 +1567,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>api_frequent_use_choices</t>
+          <t>api_pricing_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>very_affordable</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Very Affordable</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>very_affordable</t>
+          <t>affordable</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Very Affordable</t>
+          <t>Affordable</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>affordable</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Affordable</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>expensive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Expensive</t>
         </is>
       </c>
     </row>
@@ -1652,29 +1652,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>expensive</t>
+          <t>extremely_expensive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Expensive</t>
+          <t>Extremely Expensive</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>api_pricing_choices</t>
+          <t>api_security_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>extremely_expensive</t>
+          <t>very_secure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Extremely Expensive</t>
+          <t>Very Secure</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>very_secure</t>
+          <t>secure</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Very Secure</t>
+          <t>Secure</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>secure</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Secure</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>not_secure</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Not Secure</t>
         </is>
       </c>
     </row>
@@ -1737,29 +1737,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>not_secure</t>
+          <t>not_at_all_secure</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Not Secure</t>
+          <t>Not at all Secure</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>api_security_choices</t>
+          <t>api_usability_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>not_at_all_secure</t>
+          <t>very_user-friendly</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not at all Secure</t>
+          <t>Very User-Friendly</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>very_user-friendly</t>
+          <t>user-friendly</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Very User-Friendly</t>
+          <t>User-Friendly</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>user-friendly</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>User-Friendly</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>not_user-friendly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Not User-Friendly</t>
         </is>
       </c>
     </row>
@@ -1822,29 +1822,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>not_user-friendly</t>
+          <t>not_at_all_user-friendly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not User-Friendly</t>
+          <t>Not at all User-Friendly</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>api_usability_choices</t>
+          <t>api_usability_features_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>not_at_all_user-friendly</t>
+          <t>clear_and_concise_documentation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Not at all User-Friendly</t>
+          <t>Clear and concise documentation</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>clear_and_concise_documentation</t>
+          <t>intuitive_api_design</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Clear and concise documentation</t>
+          <t>Intuitive API design</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>intuitive_api_design</t>
+          <t>easy-to-use_api_keys</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Intuitive API design</t>
+          <t>Easy-to-use API keys</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>easy-to-use_api_keys</t>
+          <t>api_keys_with_a_usage_policy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Easy-to-use API keys</t>
+          <t>API keys with a usage policy</t>
         </is>
       </c>
     </row>
@@ -1907,29 +1907,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>api_keys_with_a_usage_policy</t>
+          <t>api_keys_with_a_refresh_token</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>API keys with a usage policy</t>
+          <t>API keys with a refresh token</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>api_usability_features_choices</t>
+          <t>api_developers_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>api_keys_with_a_refresh_token</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>API keys with a refresh token</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Very Likely</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Likely</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1992,27 +1992,10 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
-        <is>
-          <t>Not Likely</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>api_developers_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>not_at_all_likely</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>Not at all Likely</t>
         </is>
